--- a/zaini_case_audit_output/outputs/excel/06_unreadable_or_ocr_needed.xlsx
+++ b/zaini_case_audit_output/outputs/excel/06_unreadable_or_ocr_needed.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -498,6 +498,2848 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>صك الحكم رقم (4431025114) وتاريخ 1/1/1445هـ الصادر عن الدائرة الأولى بالمحكمة التجارية بجدة في الدعوى المقيدة برقم (42824717) وتاريخ 25/12/1442هـ ـ 1/1/1445هـ</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>أ. المجلد الرئيسي للقضية</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/12jTPoyQzBxOhbpog6uRie5gwB1IG-9O-/view</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>صك الحكم رقم (4630548401) وتاريخ 18/06/1446هـ الصادر عن دائرة الاستئناف الثانية بالمحكمة التجارية بجدة، والقاضي بعدم قبول الالتماس المقدم بالطلب رقم (4611037394) وتاريخ 02/06/1446ه</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>أ. المجلد الرئيسي للقضية</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1UhYnUWV8PCpkc0Tmw6cnSKqT12zerfNt/view</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>إقرار من السيدة/ عاتقة محمد يحي حرازي مؤرخ في 04/03/1445هـ، ممهور ببصمتها، بأنها أوكلت المحامِ (محمد فواز الثعلي) وكيلًا عنها، وعدم صحة الادعاء بحجزها ـ 04/03/1445هـ</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>أ. المجلد الرئيسي للقضية</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1S-JsbhtGsPL0ebxRRRzXIwqWQO6jU_du/view</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>آلية تنفيذ بتاريخ 09/02/1434هـ الموافق 22/12/2012م لدى فضيلة القاضي/ علي القريقري، قاضي التنفيذ بالمحكمة العامة بجدة [وذلك فيما يتعلق بنقل كل من طرفي النزاع الشركات التي اختص بها ك</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>أ. المجلد الرئيسي للقضية</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1Rxq8Tf2lFge44D895x_YlVhSKhhT6kAH/view</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>تقرير من شركة "صلاح الحجيلان للمحاماة والاستشارات القانونية مؤرخ في 10/02/1447هـ الموافق 04/08/2025م بشأن تقديم شكوى للديوان الملكي بمحافظة جدة للمخالفات التي وقعت عند نظر الدعوى ا</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>أ. المجلد الرئيسي للقضية</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1C05k6hSn-xQwHv2-bPMVeRY60lq1JxYn/view</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>مسودة التماس إعادة النظر المقدم على صك الاستئناف الصادر في الدعوى رقم (42824717) وتاريخ 25/12/1442هـ. ـ 25/12/1442هـ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>أ. المجلد الرئيسي للقضية</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1m8dl8PmAPDFJTVs25MmTH7SZAf5QFV_Y/view</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>طلب إعادة فتح الشكوى المقيدة برقم (199058) وتاريخ 18/06/1445هـ لدى المجلس الأعلى للقضاء ـ 18/06/1445هـ</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>أ. المجلد الرئيسي للقضية</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1TnwCWqP5WHA2ZXwy0GFbsx9DY9JuC_Io/view</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>تقرير العيوطي — وُجد بتاريخ 11/06/2026م ضمن مجلد مرفقات مذكرة الالتماس بين المورث وعبد الله آبار، وتقترح الدراسة نقض تقرير أبو غزالة به ـ —</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>أ. المجلد الرئيسي للقضية</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/14UdnHAbZOv9SZXnO3mMrkPePnXfEQFu9/view</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>تفاصيل إخطار المطالبة المالية بمبلغ 96,779,270</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1TzsNmsfPLd1D-ds7zyE_xKKPfZtMZNNJ/view</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>تفاصيل دعوى عدنان ضد أسامة ـ موعدها 03-01-1443</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/11QGSfb1w-5zv2-KbXXjnYjxiVuC5emhU/view</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>تفاصيل موعد دعوى عدنان ضد أسامة</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/16iGZNcIRkbpInVx0xqe0OqDoiD9F0dB4/view</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>تقديم التماس إعادة نظر في القضية من عدنان وعاتقة ـ 03-12-2024</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1dhRkC4FzkY9jUNzGm-AukbqQboQ9q-2t/view</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>تقرير جلسة القضية ـ 17-12-2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1BA4LTa4WzLrPM7d3X91DRrIO2gqYpJgi/view</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>مذكرة جوابية على المدعي ـ 02-09-1447</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>نص ضئيل/فارغ</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1JSlPkKqEnnaJVucKZYiQ19CX_HxKw3My/view</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>حكم نهائي بنقض حكم إبراء الذمة ـ 22-07-1447</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1TOjPciWFiww2D2rsm57qGXkLL-QlSToP/view</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>طلب النقض الأخير ـ 07-10-1447</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>نص ضئيل/فارغ</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1JsER2PVyIe5q3zXv3zAURxA-JkYXe3qs/view</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>طلب النقض من المحكمة العليا ـ 25-02-1445</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1YZch0mcY3_pGTtMtaN5a0cqqNAUqO7Q2/view</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>مذكرة التماس إلحاقية ـ 08-08-1445</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1z3cWsKqImdcuh0EpjGqR3rM2xw5aHgsT/view</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>مذكرة التماس الشهري 13-07-1445 ومرفقاتها</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>نص ضئيل/فارغ</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1HVbLJm6BQ4picvDOwVgvqMGPcBQNlvdZ/view</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>مذكرة إلحاقية على التماس الشيخ أسامة</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1q_HFBphb1eUvasmZs2w5IXBcC--BuaHL/view</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>مذكرة النقض للعليا 10-04-1445 ـ مرفق عقود التخارج</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1x6jb5RIYxxQpbQqNsTYhpwnGf4g5GoGJ/view</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>مذكرة جوابية ـ 16-08-1445</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/16KPeg8Q57KIeFlKlgKFIQpZfj3EhMvZT/view</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>مذكرة جوابية من الملتمس ضدهم (عدنان وعاتقة)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1mYbMRrqkZYca6OZBZ1x8QW09puKH645z/view</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>مرفق 8 ـ مذكرة أبو راشد ـ 25-04-1443</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1UgLzFge8qYnoXnkMh7EWqMVaEMajlkC4/view</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>التماس في الدعوى ـ نسخة ثانية</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1U-DWBW5EmqXWmY6UP4zza2EGeLuHN8Io/view</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>جزء من مسحوبات مصروفات الشيخ أحمد</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ز. مرفقات مذكرة الالتماس ـ أُرفقت 06-08-1445 (5 ملفات)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/16Ntp_ehFpXV_QiX0uU0f2iPoQ87ivLxs/view</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>جزء من مصروفات فيلا الوادي</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ز. مرفقات مذكرة الالتماس ـ أُرفقت 06-08-1445 (5 ملفات)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1V9aM64Q773mHIW0cRKQMqfAc8aIokWGs/view</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>مرفق (1) القروض (zip)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ح. مرفقات مصروفات الشيخ أحمد وقت الحجز (3 ملفات + 3 مجلدات داخلية)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1U9uKQ8WpgoektR7ems9tz5-I3UFy6Dc-/view</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>المسحوبات 1431 (zip)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ح-1. المسحوبات (8 ملفات)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1TaZlnYqoYKoRASsD8_QuRDuxqDPMSGfB/view</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>المسحوبات 1432 (zip)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ح-1. المسحوبات (8 ملفات)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1u1p07uJYvSMmG1zHbhBHZTMOpNjyMq47/view</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>المسحوبات 1433 (zip)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ح-1. المسحوبات (8 ملفات)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>نص ضئيل/فارغ</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1Kwq7q1_aN_YgE1Hxk-A3DjG4xMZkzS1M/view</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>المسحوبات 1434 (zip)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ح-1. المسحوبات (8 ملفات)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>نص ضئيل/فارغ</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1F7QvZkaWmAuP--ItuTYRFvlWt8QjTlQw/view</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>المسحوبات 1435 (zip)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ح-1. المسحوبات (8 ملفات)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1BU--kLmXmZjBheO12Zohj7_xl4EgKJPv/view</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>المسحوبات 1436 (zip)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ح-1. المسحوبات (8 ملفات)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>نص ضئيل/فارغ</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1LxIWcYRRnnGiCJpgxVhOvu7yLZC6Y0Pk/view</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>المسحوبات 2015 (zip)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ح-1. المسحوبات (8 ملفات)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1ZGXAH_IzT9zrzyaxGPpVkIpLBH5FORLB/view</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1431 (zip)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ح-2. المزرعة (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1pBt6r5jJ8yOJw8mwgBFVu46bKcbQ-PdM/view</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1432 (zip)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ح-2. المزرعة (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1Yc4pUN7yi_sRmcE8YKPidyscrCXG9mO-/view</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1433 (zip)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ح-2. المزرعة (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1jghsPBczcYyih79TCVOrl7UbzH5rKET5/view</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1434 (zip)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ح-2. المزرعة (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1Vw469zD1e5Q9KUlUjRAO4x6m2oB1qqMM/view</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1435 (zip)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ح-2. المزرعة (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>نص ضئيل/فارغ</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1Hhm9p0FlVa4m5mpt8ZAMzbkQ5EOLhh9o/view</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1436 (zip)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ح-2. المزرعة (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>نص ضئيل/فارغ</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1RGOZ33jzhFIi8_3uIkTviQ670XF1dVg_/view</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>مصاريف المزرعة (Excel)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ح-2. المزرعة (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1SNh5aI1IhHNBS5S2wg5b6AAb_osujWDK/view</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>فلة الوادي 1431 (rar)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ح-3. فلة الوادي (5 ملفات)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>نص ضئيل/فارغ</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1MRMCMbvZydkT1uXnciSQIFbEkhyeM5Jc/view</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>فلة الوادي 1432 (rar)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ح-3. فلة الوادي (5 ملفات)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1ydRIblgIFqUC42IjpF47n6hZAAMreeml/view</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>فلة الوادي 1433 (rar)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ح-3. فلة الوادي (5 ملفات)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1iWem4i_dljVasd3n7xoluUzotsNrSh8B/view</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>فلة الوادي 2015 (rar)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ح-3. فلة الوادي (5 ملفات)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1WUZ01OMDTjsU_b1X41ihwABmKmeD9BPQ/view</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>مصاريف فيلا الوادي (Excel)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ح-3. فلة الوادي (5 ملفات)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1lXSmR7XFizz6MJQKzmkoCz1BmFc0kNCB/view</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>صورة تقديم الشكوى</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>نص ضئيل/فارغ</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1R63mMu_oZks5DNjlO0gFq8D8k6uHD4DT/view</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>موجز الشكوى للمجلس الأعلى</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>نص ضئيل/فارغ</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1Lsz2NG_acc1g_BL7VDEJy9BD6ZGscELg/view</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>شكوى لوزير العدل (وورد)</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/180gGxs0eNvNmvOAkILRmwFNTqkaI4tiP/view</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>شكوى لوزير العدل ـ 13-11-1445</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>نص ضئيل/فارغ</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1R77OSQfzc29NIkq84RTxHSDhg60gFwcr/view</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>صورة تقديم 21-05-2024 (3)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1V6hiunw2O1ZPkYVKzawoxTx9TrqmP2pw/view</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>شكوى لوزير العدل 13-11-1445 ومرفقاتها</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1U3bYf5KLk19hdBWRa1WYwbwhAMJvOY7m/view</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>طلب إعادة فتح الشكوى (صورة)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1piRGnIrlALLMuPsl2RDETl-GPkM-7Ol4/view</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>الشكوى ومرفقاتها ـ 29-10-2024</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1qR8qS40taRQojtf7_fNKiVec3pIdPBML/view</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>تفاصيل طلب موعد مع وزير العدل ـ 19-06-1445</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>نص ضئيل/فارغ</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1LiTuA3nEHgYZR98cBPGolr9SFr0Hf5Ho/view</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ملخص الشكوى لولي العهد (وورد)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1TXwIiZOBvKF-HbFxAhXw1rK0-p1UmXVy/view</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>مذكرة الالتماس ومرفقاتها</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>س. مذكرة التماس المحامي الشهري ـ 13-07-1445 (ملف واحد)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>not_retrieved</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>غير مقروء</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>OCR غير متاح في البيئة</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1drvTbOtOVH14FiHvGQIOSguiTg3wJiPI/view</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/zaini_case_audit_output/outputs/excel/06_unreadable_or_ocr_needed.xlsx
+++ b/zaini_case_audit_output/outputs/excel/06_unreadable_or_ocr_needed.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -526,11 +526,7 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>OCR غير متاح في البيئة</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>https://drive.google.com/file/d/1C05k6hSn-xQwHv2-bPMVeRY60lq1JxYn/view</t>
@@ -575,11 +571,7 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>OCR غير متاح في البيئة</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>https://drive.google.com/file/d/11QGSfb1w-5zv2-KbXXjnYjxiVuC5emhU/view</t>
@@ -624,11 +616,7 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>OCR غير متاح في البيئة</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>https://drive.google.com/file/d/16iGZNcIRkbpInVx0xqe0OqDoiD9F0dB4/view</t>
@@ -673,11 +661,7 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>OCR غير متاح في البيئة</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>https://drive.google.com/file/d/1dhRkC4FzkY9jUNzGm-AukbqQboQ9q-2t/view</t>
@@ -722,11 +706,7 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>OCR غير متاح في البيئة</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>https://drive.google.com/file/d/1BA4LTa4WzLrPM7d3X91DRrIO2gqYpJgi/view</t>
@@ -779,11 +759,7 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>OCR غير متاح في البيئة</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>https://drive.google.com/file/d/1JsER2PVyIe5q3zXv3zAURxA-JkYXe3qs/view?usp=drivesdk</t>
@@ -828,11 +804,7 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>OCR غير متاح في البيئة</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>https://drive.google.com/file/d/1U9uKQ8WpgoektR7ems9tz5-I3UFy6Dc-/view</t>
@@ -877,11 +849,7 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>OCR غير متاح في البيئة</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>https://drive.google.com/file/d/1TaZlnYqoYKoRASsD8_QuRDuxqDPMSGfB/view</t>
@@ -926,11 +894,7 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>OCR غير متاح في البيئة</t>
-        </is>
-      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>https://drive.google.com/file/d/1u1p07uJYvSMmG1zHbhBHZTMOpNjyMq47/view</t>
@@ -975,11 +939,7 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>OCR غير متاح في البيئة</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>https://drive.google.com/file/d/1Kwq7q1_aN_YgE1Hxk-A3DjG4xMZkzS1M/view</t>
@@ -999,24 +959,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>المسحوبات 1434 (zip)</t>
+          <t>مزرعة الوادي 1431 (zip)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ح-1. المسحوبات (8 ملفات)</t>
+          <t>ح-2. المزرعة (7 ملفات)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>not_retrieved</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>نص ضئيل/فارغ</t>
+          <t>غير مقروء</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1024,14 +984,10 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>OCR غير متاح في البيئة</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1F7QvZkaWmAuP--ItuTYRFvlWt8QjTlQw/view</t>
+          <t>https://drive.google.com/file/d/1pBt6r5jJ8yOJw8mwgBFVu46bKcbQ-PdM/view</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1048,12 +1004,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>المسحوبات 1435 (zip)</t>
+          <t>مزرعة الوادي 1432 (zip)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ح-1. المسحوبات (8 ملفات)</t>
+          <t>ح-2. المزرعة (7 ملفات)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -1073,14 +1029,10 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>OCR غير متاح في البيئة</t>
-        </is>
-      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1BU--kLmXmZjBheO12Zohj7_xl4EgKJPv/view</t>
+          <t>https://drive.google.com/file/d/1Yc4pUN7yi_sRmcE8YKPidyscrCXG9mO-/view</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1097,12 +1049,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>المسحوبات 1436 (zip)</t>
+          <t>فلة الوادي 1431 (rar)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ح-1. المسحوبات (8 ملفات)</t>
+          <t>ح-3. فلة الوادي (5 ملفات)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -1122,14 +1074,10 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>OCR غير متاح في البيئة</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1LxIWcYRRnnGiCJpgxVhOvu7yLZC6Y0Pk/view</t>
+          <t>https://drive.google.com/file/d/1MRMCMbvZydkT1uXnciSQIFbEkhyeM5Jc/view</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1146,12 +1094,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>المسحوبات 2015 (zip)</t>
+          <t>فلة الوادي 1432 (rar)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ح-1. المسحوبات (8 ملفات)</t>
+          <t>ح-3. فلة الوادي (5 ملفات)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -1171,14 +1119,10 @@
           <t>نعم</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>OCR غير متاح في البيئة</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ZGXAH_IzT9zrzyaxGPpVkIpLBH5FORLB/view</t>
+          <t>https://drive.google.com/file/d/1ydRIblgIFqUC42IjpF47n6hZAAMreeml/view</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1187,594 +1131,6 @@
         </is>
       </c>
       <c r="K15" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>مزرعة الوادي 1431 (zip)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>ح-2. المزرعة (7 ملفات)</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>not_retrieved</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>غير مقروء</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>OCR غير متاح في البيئة</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1pBt6r5jJ8yOJw8mwgBFVu46bKcbQ-PdM/view</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>مزرعة الوادي 1432 (zip)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ح-2. المزرعة (7 ملفات)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>not_retrieved</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>غير مقروء</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>OCR غير متاح في البيئة</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1Yc4pUN7yi_sRmcE8YKPidyscrCXG9mO-/view</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>مزرعة الوادي 1433 (zip)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ح-2. المزرعة (7 ملفات)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>not_retrieved</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>غير مقروء</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>OCR غير متاح في البيئة</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1jghsPBczcYyih79TCVOrl7UbzH5rKET5/view</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>مزرعة الوادي 1434 (zip)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>ح-2. المزرعة (7 ملفات)</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>not_retrieved</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>غير مقروء</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>OCR غير متاح في البيئة</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1Vw469zD1e5Q9KUlUjRAO4x6m2oB1qqMM/view</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>مزرعة الوادي 1435 (zip)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ح-2. المزرعة (7 ملفات)</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>empty</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>نص ضئيل/فارغ</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>OCR غير متاح في البيئة</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1Hhm9p0FlVa4m5mpt8ZAMzbkQ5EOLhh9o/view</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>مزرعة الوادي 1436 (zip)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>ح-2. المزرعة (7 ملفات)</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>empty</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>نص ضئيل/فارغ</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>OCR غير متاح في البيئة</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1RGOZ33jzhFIi8_3uIkTviQ670XF1dVg_/view</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>فلة الوادي 1431 (rar)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>ح-3. فلة الوادي (5 ملفات)</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>empty</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>نص ضئيل/فارغ</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>OCR غير متاح في البيئة</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1MRMCMbvZydkT1uXnciSQIFbEkhyeM5Jc/view</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>فلة الوادي 1432 (rar)</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>ح-3. فلة الوادي (5 ملفات)</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>not_retrieved</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>غير مقروء</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>OCR غير متاح في البيئة</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1ydRIblgIFqUC42IjpF47n6hZAAMreeml/view</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>فلة الوادي 1433 (rar)</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>ح-3. فلة الوادي (5 ملفات)</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>not_retrieved</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>غير مقروء</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>OCR غير متاح في البيئة</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1iWem4i_dljVasd3n7xoluUzotsNrSh8B/view</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>فلة الوادي 2015 (rar)</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>ح-3. فلة الوادي (5 ملفات)</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>not_retrieved</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>غير مقروء</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>OCR غير متاح في البيئة</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1WUZ01OMDTjsU_b1X41ihwABmKmeD9BPQ/view</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>صورة تقديم الشكوى</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>empty</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>نص ضئيل/فارغ</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>OCR غير متاح في البيئة</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1R63mMu_oZks5DNjlO0gFq8D8k6uHD4DT/view</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>صورة تقديم 21-05-2024 (3)</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>not_retrieved</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>غير مقروء</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>OCR غير متاح في البيئة</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1V6hiunw2O1ZPkYVKzawoxTx9TrqmP2pw/view</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
         <is>
           <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
         </is>

--- a/zaini_case_audit_output/outputs/excel/06_unreadable_or_ocr_needed.xlsx
+++ b/zaini_case_audit_output/outputs/excel/06_unreadable_or_ocr_needed.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -726,32 +726,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>طلب النقض الاحير المقدم في 07-10-1447 ـ القضية 42824717.pdf</t>
+          <t>مرفق (1) القروض (zip)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>pdf</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>182371</t>
-        </is>
-      </c>
+          <t>ح. مرفقات مصروفات الشيخ أحمد وقت الحجز (3 ملفات + 3 مجلدات داخلية)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>not_retrieved</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>نص ضئيل/فارغ</t>
+          <t>غير مقروء</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -762,7 +754,7 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1JsER2PVyIe5q3zXv3zAURxA-JkYXe3qs/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1U9uKQ8WpgoektR7ems9tz5-I3UFy6Dc-/view</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -779,12 +771,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>مرفق (1) القروض (zip)</t>
+          <t>المسحوبات 1431 (zip)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ح. مرفقات مصروفات الشيخ أحمد وقت الحجز (3 ملفات + 3 مجلدات داخلية)</t>
+          <t>ح-1. المسحوبات (8 ملفات)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -807,7 +799,7 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1U9uKQ8WpgoektR7ems9tz5-I3UFy6Dc-/view</t>
+          <t>https://drive.google.com/file/d/1TaZlnYqoYKoRASsD8_QuRDuxqDPMSGfB/view</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -824,7 +816,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>المسحوبات 1431 (zip)</t>
+          <t>المسحوبات 1432 (zip)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -852,7 +844,7 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1TaZlnYqoYKoRASsD8_QuRDuxqDPMSGfB/view</t>
+          <t>https://drive.google.com/file/d/1u1p07uJYvSMmG1zHbhBHZTMOpNjyMq47/view</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -869,7 +861,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>المسحوبات 1432 (zip)</t>
+          <t>المسحوبات 1433 (zip)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -881,12 +873,12 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>not_retrieved</t>
+          <t>empty</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>غير مقروء</t>
+          <t>نص ضئيل/فارغ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -897,7 +889,7 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1u1p07uJYvSMmG1zHbhBHZTMOpNjyMq47/view</t>
+          <t>https://drive.google.com/file/d/1Kwq7q1_aN_YgE1Hxk-A3DjG4xMZkzS1M/view</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -914,24 +906,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>المسحوبات 1433 (zip)</t>
+          <t>مزرعة الوادي 1431 (zip)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ح-1. المسحوبات (8 ملفات)</t>
+          <t>ح-2. المزرعة (7 ملفات)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>not_retrieved</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>نص ضئيل/فارغ</t>
+          <t>غير مقروء</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -942,7 +934,7 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Kwq7q1_aN_YgE1Hxk-A3DjG4xMZkzS1M/view</t>
+          <t>https://drive.google.com/file/d/1pBt6r5jJ8yOJw8mwgBFVu46bKcbQ-PdM/view</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -959,7 +951,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>مزرعة الوادي 1431 (zip)</t>
+          <t>مزرعة الوادي 1432 (zip)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -987,7 +979,7 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1pBt6r5jJ8yOJw8mwgBFVu46bKcbQ-PdM/view</t>
+          <t>https://drive.google.com/file/d/1Yc4pUN7yi_sRmcE8YKPidyscrCXG9mO-/view</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1004,24 +996,24 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>مزرعة الوادي 1432 (zip)</t>
+          <t>فلة الوادي 1431 (rar)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ح-2. المزرعة (7 ملفات)</t>
+          <t>ح-3. فلة الوادي (5 ملفات)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>not_retrieved</t>
+          <t>empty</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>غير مقروء</t>
+          <t>نص ضئيل/فارغ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1032,7 +1024,7 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Yc4pUN7yi_sRmcE8YKPidyscrCXG9mO-/view</t>
+          <t>https://drive.google.com/file/d/1MRMCMbvZydkT1uXnciSQIFbEkhyeM5Jc/view</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1049,7 +1041,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>فلة الوادي 1431 (rar)</t>
+          <t>فلة الوادي 1432 (rar)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1061,12 +1053,12 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>not_retrieved</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>نص ضئيل/فارغ</t>
+          <t>غير مقروء</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1077,7 +1069,7 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1MRMCMbvZydkT1uXnciSQIFbEkhyeM5Jc/view</t>
+          <t>https://drive.google.com/file/d/1ydRIblgIFqUC42IjpF47n6hZAAMreeml/view</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1086,51 +1078,6 @@
         </is>
       </c>
       <c r="K14" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>فلة الوادي 1432 (rar)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>ح-3. فلة الوادي (5 ملفات)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>not_retrieved</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>غير مقروء</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1ydRIblgIFqUC42IjpF47n6hZAAMreeml/view</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
         <is>
           <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
         </is>
